--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6803_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6803_SW2.xlsx
@@ -1023,7 +1023,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>Air-Way FF6803 (s37, double-pass 2026-10-15, parts.air-way.com/api/series/37, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p17 FS6803-08-08-08-NWO-FG (ORFS-p017-t03); FORGED part: Air-Way NON-forged row FF6803-8-8-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length = gen_straight2 FSM_MEAS (Brennan FS2403-08-08); on the forged legs the thread major runs to the end length and steps down to the hex flats (Brennan FS6500 / FS6801 / FS2701-08 forged legs) - the end stands proud of the flats; hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
+          <t>Air-Way FF6803 (s37, double-pass 2026-10-15, parts.air-way.com/api/series/37, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p17 FS6803-08-08-08-NWO-FG (ORFS-p017-t03); FORGED part: Air-Way NON-forged row FF6803-8-8-8 NWO, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); adjustable ORB stud on an FS part (Brennan FS6801-08-08-NWO-FG): neck, lock nut (0.41 thick, hex = the row S3), washer and O-ring undercut measured on the -08 pilot (NWO_FS; washer and undercut = the 6801 library NWO_MEAS); washer face at Air-Way L11 / L14 from the crossing (stud = tip -&gt; washer face, Q-FS-ORBSTUD (a)); thread from the tip to the undercut (the extra stud length is thread); thread major, undercut dia = the ORB end library; O-ring not modelled; adjustable ORB stud end (nut, washer, O-ring) - Brennan 6801-XX-XX-NWO-FG STEPs, one per ORB size -02..-32: from the body face (Air-Way LEG minus ORB_I3, = Brennan on every STEP) a round neck, the locknut (hex = Air-Way HEXB = Brennan, measured thickness, both faces chamfered 15deg to the face from the across-flats circle as MEASURED on all 12 STEPs - drawn as a revolved envelope cut to the hexagon, flats normal to Z; chamfer start drawn 0.005 outside the flats circle to avoid a tangent edge: ASSUMPTION, cosmetic), the backup washer (measured OD and thickness), the O-ring undercut (root = Air-Way groove dia = Brennan) and the male ORB thread (Air-Way thread length, Thread feature); locknut, washer and O-ring are one solid with the body, as on the Brennan STEPs (O-ring not drawn); the nut sits where Brennan shows it (backed off against the washer); no tip chamfer (as on the fixed ORB ends); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">

--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6803_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6803_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
